--- a/need/数据表结构.xlsx
+++ b/need/数据表结构.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28213"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28221"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HYun\OneDrive\Desktop\图书管理系统\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B6D407-594A-42F3-ACE0-2CD1C7E48B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08BF861-630D-467F-8354-DD46E7E51FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="130">
   <si>
     <t>字段名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -370,14 +370,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>借阅记录表lend_records</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>归还记录表return_records</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>推荐图书表recommend_books</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -509,6 +501,46 @@
   </si>
   <si>
     <t>用户历史借书数量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史借阅记录表lend_records</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史归还记录表return_records</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前借阅记录表cur_lend_records</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>_</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会话记录表session_state</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会话名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会话id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uuid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -619,6 +651,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -626,9 +661,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -911,7 +943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.109375" style="2" bestFit="1" customWidth="1"/>
@@ -921,13 +953,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -995,10 +1027,10 @@
     </row>
     <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
@@ -1007,15 +1039,15 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -1024,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1067,13 +1099,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1154,7 +1186,7 @@
     </row>
     <row r="19" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -1169,7 +1201,7 @@
     </row>
     <row r="20" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
@@ -1278,7 +1310,7 @@
     </row>
     <row r="27" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>25</v>
@@ -1294,13 +1326,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1361,12 +1393,12 @@
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
@@ -1398,7 +1430,7 @@
     </row>
     <row r="37" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
@@ -1412,13 +1444,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
+      <c r="A40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -1479,12 +1511,12 @@
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>6</v>
@@ -1499,7 +1531,7 @@
     </row>
     <row r="46" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>6</v>
@@ -1531,29 +1563,29 @@
     </row>
     <row r="48" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
+      <c r="A51" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
     </row>
     <row r="52" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -1574,7 +1606,7 @@
     </row>
     <row r="53" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>69</v>
@@ -1599,7 +1631,7 @@
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1665,13 +1697,13 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
+      <c r="A61" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
@@ -1692,22 +1724,22 @@
     </row>
     <row r="63" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>6</v>
@@ -1717,12 +1749,12 @@
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>6</v>
@@ -1732,12 +1764,12 @@
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>6</v>
@@ -1747,85 +1779,88 @@
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-    </row>
-    <row r="70" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B72" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B71" s="1" t="s">
+      <c r="I72" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>6</v>
@@ -1835,12 +1870,12 @@
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>6</v>
@@ -1850,68 +1885,68 @@
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="5"/>
-    </row>
-    <row r="79" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D81" s="1"/>
       <c r="E81" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>6</v>
@@ -1919,14 +1954,16 @@
       <c r="C82" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D82" s="1"/>
+      <c r="D82" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E82" s="1" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>6</v>
@@ -1936,12 +1973,12 @@
       </c>
       <c r="D83" s="1"/>
       <c r="E83" s="1" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>6</v>
@@ -1949,59 +1986,55 @@
       <c r="C84" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="D84" s="1"/>
       <c r="E84" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="5"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="88" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A88" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="6"/>
     </row>
     <row r="89" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D89" s="1">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>25</v>
@@ -2009,58 +2042,240 @@
       <c r="C90" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D90" s="1">
-        <v>0</v>
-      </c>
+      <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D91" s="1">
-        <v>0</v>
-      </c>
+      <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="6"/>
+    </row>
+    <row r="98" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="1">
+      <c r="C99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="1">
         <v>0</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="E99" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="1">
+        <v>0</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="1">
+        <v>0</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="105" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A87:E87"/>
+  <mergeCells count="11">
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A78:E78"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/need/数据表结构.xlsx
+++ b/need/数据表结构.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28221"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28224"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HYun\OneDrive\Desktop\图书管理系统\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08BF861-630D-467F-8354-DD46E7E51FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E66536C-771D-45CB-8D33-8E14337B4F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1992" yWindow="2100" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="148">
   <si>
     <t>字段名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -541,6 +541,78 @@
   </si>
   <si>
     <t>uuid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员账户admim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin_password</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin_role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin/Admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身份(a普通，A高级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjust_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整编号（自增字段）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjust_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjust_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjust_isbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整书的isbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整书的书名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adjust_content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调整内容（增,删..）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>书籍调整表adjust_books</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -651,9 +723,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -661,6 +730,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -943,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.109375" style="2" bestFit="1" customWidth="1"/>
@@ -953,13 +1025,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1099,13 +1171,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1326,13 +1398,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1444,13 +1516,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -1579,13 +1651,13 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
@@ -1697,13 +1769,13 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
     </row>
     <row r="62" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
@@ -1815,13 +1887,13 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
     </row>
     <row r="72" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
@@ -1904,13 +1976,13 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
     </row>
     <row r="80" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
@@ -2007,13 +2079,13 @@
       </c>
     </row>
     <row r="88" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="6"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
@@ -2110,13 +2182,13 @@
       </c>
     </row>
     <row r="97" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="6"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="4"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="5"/>
     </row>
     <row r="98" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
@@ -2204,13 +2276,13 @@
       </c>
     </row>
     <row r="105" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
     </row>
     <row r="106" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
@@ -2263,19 +2335,195 @@
         <v>128</v>
       </c>
     </row>
+    <row r="111" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="5"/>
+    </row>
+    <row r="112" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+    </row>
+    <row r="119" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A105:E105"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A97:E97"/>
+  <mergeCells count="13">
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A88:E88"/>
-    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A105:E105"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A97:E97"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
